--- a/AAII_Financials/Quarterly/ABAT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ABAT_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>ABAT</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,61 +656,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -738,8 +745,14 @@
       <c r="K8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -767,8 +780,14 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -796,8 +815,14 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -809,37 +834,45 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E12" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F12" s="3">
         <v>4700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>2100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>2300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>1400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -867,37 +900,49 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -925,8 +970,14 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -935,37 +986,45 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F17" s="3">
         <v>7200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>5600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>6200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>2600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>6800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>2800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>4100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -973,28 +1032,34 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="G18" s="3">
         <v>-5600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-6200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-2600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-6800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-2800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-4100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1006,8 +1071,10 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1018,25 +1085,31 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1044,48 +1117,54 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="G21" s="3">
         <v>-5600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-6200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-2400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-6800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-2600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-4100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E22" s="3">
+        <v>800</v>
+      </c>
+      <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>4</v>
+      <c r="G22" s="3">
+        <v>0</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -1093,37 +1172,49 @@
       <c r="K22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-7100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-5600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-6200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-2400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-6900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-2600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-4100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1151,8 +1242,14 @@
       <c r="K24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1180,66 +1277,84 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-7100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-5600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-6200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-2400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-6900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-2600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-4100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-7100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-5600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-6200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-2400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-6900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-2600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-4100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1267,8 +1382,14 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1296,8 +1417,14 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1325,8 +1452,14 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1354,8 +1487,14 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1366,54 +1505,66 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-7100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-5600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-6200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-2400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-6900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-2600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-4100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1441,71 +1592,89 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-7100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-5600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-6200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-2400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-6900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-2600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-4100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1517,8 +1686,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1530,45 +1701,53 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F41" s="3">
         <v>2300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>12600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>11400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>20900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>29000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>36300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>42500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>45900</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -1582,55 +1761,67 @@
       <c r="I42" s="3">
         <v>0</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F43" s="3">
         <v>700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>400</v>
+      </c>
+      <c r="F44" s="3">
         <v>100</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>4</v>
       </c>
@@ -1646,66 +1837,84 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F45" s="3">
         <v>1600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1600</v>
-      </c>
-      <c r="F45" s="3">
-        <v>900</v>
-      </c>
-      <c r="G45" s="3">
-        <v>800</v>
       </c>
       <c r="H45" s="3">
         <v>900</v>
       </c>
       <c r="I45" s="3">
+        <v>800</v>
+      </c>
+      <c r="J45" s="3">
+        <v>900</v>
+      </c>
+      <c r="K45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>8400</v>
+      </c>
+      <c r="F46" s="3">
         <v>4800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>14400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>13700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>21700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>29900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>36800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>44400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>47700</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1733,45 +1942,57 @@
       <c r="K47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>72400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>69400</v>
+      </c>
+      <c r="F48" s="3">
         <v>38300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>33000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>30100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>28200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>19100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>16000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>12000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>3900</v>
+        <v>4600</v>
       </c>
       <c r="E49" s="3">
-        <v>3900</v>
+        <v>4600</v>
       </c>
       <c r="F49" s="3">
         <v>3900</v>
@@ -1783,16 +2004,22 @@
         <v>3900</v>
       </c>
       <c r="I49" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="J49" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="K49" s="3">
         <v>3800</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3">
+        <v>3800</v>
+      </c>
+      <c r="M49" s="3">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1820,8 +2047,14 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1849,23 +2082,29 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>300</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F52" s="3">
         <v>27700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>6100</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H52" s="3" t="s">
         <v>4</v>
       </c>
@@ -1878,8 +2117,14 @@
       <c r="K52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1907,37 +2152,49 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>88900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>83900</v>
+      </c>
+      <c r="F54" s="3">
         <v>74700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>57400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>47600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>53800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>52900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>56600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>60200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>60200</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1949,8 +2206,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1962,49 +2221,57 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F57" s="3">
         <v>7300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>3200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>6200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>3000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>3400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>4400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>17200</v>
+      </c>
+      <c r="F58" s="3">
         <v>6000</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G58" s="3" t="s">
         <v>4</v>
       </c>
@@ -2020,16 +2287,22 @@
       <c r="K58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>100</v>
+        <v>2100</v>
       </c>
       <c r="E59" s="3">
-        <v>100</v>
+        <v>3200</v>
       </c>
       <c r="F59" s="3">
         <v>100</v>
@@ -2041,45 +2314,57 @@
         <v>100</v>
       </c>
       <c r="I59" s="3">
+        <v>100</v>
+      </c>
+      <c r="J59" s="3">
+        <v>100</v>
+      </c>
+      <c r="K59" s="3">
         <v>300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>23000</v>
+      </c>
+      <c r="F60" s="3">
         <v>13400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>6300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>3700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>4700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2087,7 +2372,7 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -2107,16 +2392,22 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>100</v>
-      </c>
-      <c r="E62" s="3">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F62" s="3">
         <v>100</v>
@@ -2125,19 +2416,25 @@
         <v>100</v>
       </c>
       <c r="H62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J62" s="3">
         <v>200</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K62" s="3">
+        <v>200</v>
+      </c>
+      <c r="L62" s="3">
+        <v>200</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2165,8 +2462,14 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2194,8 +2497,14 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2223,37 +2532,49 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>24700</v>
+      </c>
+      <c r="F66" s="3">
         <v>13400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>3400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>6500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>3200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>4900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2265,8 +2586,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2294,8 +2617,14 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2323,8 +2652,14 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2347,13 +2682,19 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
         <v>300</v>
       </c>
-      <c r="K70" s="3">
+      <c r="M70" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2381,37 +2722,49 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-176500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-167200</v>
+      </c>
+      <c r="F72" s="3">
         <v>-160000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-152900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-147300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-141100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-138600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-131800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-129200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-125100</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2439,8 +2792,14 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2468,8 +2827,14 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2497,37 +2862,49 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>66600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>59200</v>
+      </c>
+      <c r="F76" s="3">
         <v>61200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>53900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>45900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>47300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>49600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>52700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>55100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>57400</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2555,71 +2932,89 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-7100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-5600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-6200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-2400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-6900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-2600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-4100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2631,8 +3026,10 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2660,8 +3057,14 @@
       <c r="K83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2689,8 +3092,14 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2718,8 +3127,14 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2747,8 +3162,14 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2776,8 +3197,14 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2805,37 +3232,49 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="F89" s="3">
         <v>-2600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-3400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-3300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-4000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-2900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-2900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2847,37 +3286,45 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="F91" s="3">
         <v>-2900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-1700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-6100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-4100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-4100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-3800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2905,8 +3352,14 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2934,37 +3387,49 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-18700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-7800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-6100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-4100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-4100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-3800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-1600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2976,8 +3441,10 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3005,8 +3472,14 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3034,8 +3507,14 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3063,8 +3542,14 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3092,37 +3577,49 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>15100</v>
+      </c>
+      <c r="F100" s="3">
         <v>11000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>12400</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>500</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>41200</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3150,33 +3647,45 @@
       <c r="K101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-10300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>1100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-9400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-8100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-7300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-6200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-3400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>33100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ABAT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ABAT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
   <si>
     <t>ABAT</t>
   </si>
@@ -656,68 +656,72 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -751,8 +755,11 @@
       <c r="M8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -786,8 +793,11 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -821,8 +831,11 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -836,43 +849,47 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>3900</v>
+        <v>5400</v>
       </c>
       <c r="E12" s="3">
+        <v>9400</v>
+      </c>
+      <c r="F12" s="3">
         <v>3400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>4700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1400</v>
-      </c>
-      <c r="K12" s="3">
-        <v>200</v>
       </c>
       <c r="L12" s="3">
         <v>200</v>
       </c>
       <c r="M12" s="3">
+        <v>200</v>
+      </c>
+      <c r="N12" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -906,8 +923,11 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -917,20 +937,20 @@
       <c r="E14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
+      <c r="H14" s="3">
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -939,10 +959,13 @@
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -976,8 +999,11 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -988,43 +1014,47 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>8200</v>
+        <v>8600</v>
       </c>
       <c r="E17" s="3">
+        <v>16800</v>
+      </c>
+      <c r="F17" s="3">
         <v>6400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1032,34 +1062,37 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-6400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-7200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-5600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-6200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-6800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1073,8 +1106,9 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1082,34 +1116,37 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1117,57 +1154,60 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-6400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-6900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-5600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-6200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-6800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-4100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="E22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F22" s="3">
         <v>800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
       <c r="H22" s="3">
         <v>0</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1178,43 +1218,49 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-9300</v>
+        <v>-10000</v>
       </c>
       <c r="E23" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="F23" s="3">
         <v>-7200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-7100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-6200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-6900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1248,8 +1294,11 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1283,78 +1332,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-9300</v>
+        <v>-10000</v>
       </c>
       <c r="E26" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="F26" s="3">
         <v>-7200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-7100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-6200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-6900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-9300</v>
+        <v>-10000</v>
       </c>
       <c r="E27" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-7200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-7100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1388,8 +1446,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1423,8 +1484,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1458,8 +1522,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1493,8 +1560,11 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1502,69 +1572,75 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-9300</v>
+        <v>-10000</v>
       </c>
       <c r="E33" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-7200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-7100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1598,83 +1674,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-9300</v>
+        <v>-10000</v>
       </c>
       <c r="E35" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-7200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-7100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1688,8 +1773,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1703,43 +1789,47 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E41" s="3">
         <v>7600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>11400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>20900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>29000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>36300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>42500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>45900</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1750,7 +1840,7 @@
         <v>100</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G42" s="3">
         <v>0</v>
@@ -1767,38 +1857,41 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>4</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>100</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
@@ -1808,8 +1901,11 @@
       <c r="M43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1817,14 +1913,14 @@
         <v>600</v>
       </c>
       <c r="E44" s="3">
+        <v>600</v>
+      </c>
+      <c r="F44" s="3">
         <v>400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>100</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H44" s="3" t="s">
         <v>4</v>
       </c>
@@ -1843,78 +1939,87 @@
       <c r="M44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1100</v>
+        <v>700</v>
       </c>
       <c r="E45" s="3">
         <v>1100</v>
       </c>
       <c r="F45" s="3">
-        <v>1600</v>
+        <v>1100</v>
       </c>
       <c r="G45" s="3">
         <v>1600</v>
       </c>
       <c r="H45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I45" s="3">
         <v>900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>400</v>
-      </c>
-      <c r="L45" s="3">
-        <v>1800</v>
       </c>
       <c r="M45" s="3">
         <v>1800</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E46" s="3">
         <v>11600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>14400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>13700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>21700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>29900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>36800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>44400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>47700</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1948,43 +2053,49 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E48" s="3">
         <v>72400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>69400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>38300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>33000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>30100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>28200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>19100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>16000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>12000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1995,7 +2106,7 @@
         <v>4600</v>
       </c>
       <c r="F49" s="3">
-        <v>3900</v>
+        <v>4600</v>
       </c>
       <c r="G49" s="3">
         <v>3900</v>
@@ -2010,7 +2121,7 @@
         <v>3900</v>
       </c>
       <c r="K49" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="L49" s="3">
         <v>3800</v>
@@ -2018,8 +2129,11 @@
       <c r="M49" s="3">
         <v>3800</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2053,8 +2167,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2088,8 +2205,11 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2097,17 +2217,17 @@
         <v>300</v>
       </c>
       <c r="E52" s="3">
+        <v>300</v>
+      </c>
+      <c r="F52" s="3">
         <v>1600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>27700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>6100</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I52" s="3" t="s">
         <v>4</v>
       </c>
@@ -2123,8 +2243,11 @@
       <c r="M52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2158,43 +2281,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>89300</v>
+      </c>
+      <c r="E54" s="3">
         <v>88900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>83900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>74700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>57400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>47600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>53800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>52900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>56600</v>
-      </c>
-      <c r="L54" s="3">
-        <v>60200</v>
       </c>
       <c r="M54" s="3">
         <v>60200</v>
       </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3">
+        <v>60200</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2208,8 +2337,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2223,58 +2353,62 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E57" s="3">
         <v>3900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E58" s="3">
         <v>16300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>17200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6000</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H58" s="3" t="s">
         <v>4</v>
       </c>
@@ -2293,19 +2427,22 @@
       <c r="M58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E59" s="3">
         <v>2100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3200</v>
-      </c>
-      <c r="F59" s="3">
-        <v>100</v>
       </c>
       <c r="G59" s="3">
         <v>100</v>
@@ -2320,51 +2457,57 @@
         <v>100</v>
       </c>
       <c r="K59" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="L59" s="3">
         <v>300</v>
       </c>
       <c r="M59" s="3">
+        <v>300</v>
+      </c>
+      <c r="N59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E60" s="3">
         <v>22300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>23000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2372,11 +2515,11 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>1700</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
@@ -2398,19 +2541,22 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F62" s="3">
-        <v>100</v>
+        <v>2200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G62" s="3">
         <v>100</v>
@@ -2422,7 +2568,7 @@
         <v>100</v>
       </c>
       <c r="J62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K62" s="3">
         <v>200</v>
@@ -2430,11 +2576,14 @@
       <c r="L62" s="3">
         <v>200</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M62" s="3">
+        <v>200</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2468,8 +2617,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2503,8 +2655,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2538,43 +2693,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E66" s="3">
         <v>22300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>24700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>13400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2588,8 +2749,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2623,8 +2785,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2658,8 +2823,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2688,13 +2856,16 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
         <v>300</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2728,43 +2899,49 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-189900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-176500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-167200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-160000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-152900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-147300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-141100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-138600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-131800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-129200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-125100</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2798,8 +2975,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2833,8 +3013,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2868,43 +3051,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>70100</v>
+      </c>
+      <c r="E76" s="3">
         <v>66600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>59200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>61200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>53900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>45900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>47300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>49600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>52700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>55100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>57400</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2938,83 +3127,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-9300</v>
+        <v>-10000</v>
       </c>
       <c r="E81" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-7200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-7100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3028,8 +3226,9 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3037,7 +3236,7 @@
         <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
@@ -3063,8 +3262,11 @@
       <c r="M83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3098,8 +3300,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3133,8 +3338,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3168,8 +3376,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3203,8 +3414,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3238,43 +3452,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-2700</v>
+        <v>-5000</v>
       </c>
       <c r="E89" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="F89" s="3">
         <v>-4800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4000</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-2900</v>
       </c>
       <c r="K89" s="3">
         <v>-2900</v>
       </c>
       <c r="L89" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="M89" s="3">
         <v>-1700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3288,43 +3508,47 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6100</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-4100</v>
       </c>
       <c r="J91" s="3">
         <v>-4100</v>
       </c>
       <c r="K91" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="L91" s="3">
         <v>-3800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3358,8 +3582,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3393,43 +3620,49 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-3600</v>
+        <v>-500</v>
       </c>
       <c r="E94" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-7300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-18700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6100</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-4100</v>
       </c>
       <c r="J94" s="3">
         <v>-4100</v>
       </c>
       <c r="K94" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="L94" s="3">
         <v>-3800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3443,8 +3676,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3478,8 +3712,11 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3513,8 +3750,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3548,8 +3788,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3583,43 +3826,49 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>8500</v>
+        <v>3900</v>
       </c>
       <c r="E100" s="3">
+        <v>23600</v>
+      </c>
+      <c r="F100" s="3">
         <v>15100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>11000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>12400</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>500</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>41200</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3653,39 +3902,45 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>2300</v>
+        <v>-1700</v>
       </c>
       <c r="E102" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F102" s="3">
         <v>3100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-10300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-8100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-7300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-6200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>33100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ABAT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ABAT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="92">
   <si>
     <t>ABAT</t>
   </si>
@@ -656,95 +656,103 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>4</v>
+      <c r="D8" s="3">
+        <v>200</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -758,16 +766,22 @@
       <c r="N8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>4</v>
+      <c r="D9" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3300</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>4</v>
@@ -796,16 +810,22 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>4</v>
+      <c r="D10" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-3000</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>4</v>
@@ -834,8 +854,14 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -850,46 +876,54 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>5400</v>
+        <v>2000</v>
       </c>
       <c r="E12" s="3">
-        <v>9400</v>
+        <v>3200</v>
       </c>
       <c r="F12" s="3">
-        <v>3400</v>
+        <v>4000</v>
       </c>
       <c r="G12" s="3">
-        <v>4700</v>
+        <v>5000</v>
       </c>
       <c r="H12" s="3">
-        <v>2100</v>
+        <v>3600</v>
       </c>
       <c r="I12" s="3">
+        <v>4100</v>
+      </c>
+      <c r="J12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K12" s="3">
         <v>2300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>1400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -926,19 +960,25 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>700</v>
+      </c>
+      <c r="E14" s="3">
+        <v>10300</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
@@ -946,34 +986,40 @@
       <c r="H14" s="3">
         <v>0</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="I14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
@@ -1002,8 +1048,14 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1015,84 +1067,98 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>12400</v>
+      </c>
+      <c r="F17" s="3">
         <v>8600</v>
       </c>
-      <c r="E17" s="3">
-        <v>16800</v>
-      </c>
-      <c r="F17" s="3">
-        <v>6400</v>
-      </c>
       <c r="G17" s="3">
-        <v>7200</v>
+        <v>10400</v>
       </c>
       <c r="H17" s="3">
+        <v>8000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>8000</v>
+      </c>
+      <c r="J17" s="3">
         <v>5600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>6200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>6800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>4100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-9800</v>
       </c>
       <c r="E18" s="3">
-        <v>-16800</v>
+        <v>-12100</v>
       </c>
       <c r="F18" s="3">
-        <v>-6400</v>
+        <v>-8600</v>
       </c>
       <c r="G18" s="3">
-        <v>-7200</v>
+        <v>-10400</v>
       </c>
       <c r="H18" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="J18" s="3">
         <v>-5600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-6200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-2600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-6800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-2800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-4100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1107,104 +1173,118 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>100</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>100</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>200</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>-8600</v>
       </c>
       <c r="E21" s="3">
-        <v>-17000</v>
+        <v>-10400</v>
       </c>
       <c r="F21" s="3">
-        <v>-6400</v>
+        <v>-8800</v>
       </c>
       <c r="G21" s="3">
-        <v>-6900</v>
+        <v>-9900</v>
       </c>
       <c r="H21" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="J21" s="3">
         <v>-5600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-6200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-2400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-6800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-2600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-4100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="E22" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="F22" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>4</v>
@@ -1212,8 +1292,8 @@
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1221,69 +1301,81 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="F23" s="3">
         <v>-10000</v>
       </c>
-      <c r="E23" s="3">
-        <v>-19100</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-7200</v>
-      </c>
       <c r="G23" s="3">
-        <v>-7100</v>
+        <v>-11800</v>
       </c>
       <c r="H23" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="J23" s="3">
         <v>-5600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-6200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-2400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-6900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-2600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-4100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1297,8 +1389,14 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1335,84 +1433,102 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-10000</v>
       </c>
-      <c r="E26" s="3">
-        <v>-19100</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-7200</v>
-      </c>
       <c r="G26" s="3">
-        <v>-7100</v>
+        <v>-11800</v>
       </c>
       <c r="H26" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="J26" s="3">
         <v>-5600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-6200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-2400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-6900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-2600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-4100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-10000</v>
       </c>
-      <c r="E27" s="3">
-        <v>-19100</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-7200</v>
-      </c>
       <c r="G27" s="3">
-        <v>-7100</v>
+        <v>-11800</v>
       </c>
       <c r="H27" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="J27" s="3">
         <v>-5600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-6200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-2400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-6900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-2600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-4100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1449,8 +1565,14 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1487,8 +1609,14 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1525,8 +1653,14 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1563,84 +1697,102 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="G32" s="3">
+        <v>500</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-10000</v>
       </c>
-      <c r="E33" s="3">
-        <v>-19100</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-7200</v>
-      </c>
       <c r="G33" s="3">
-        <v>-7100</v>
+        <v>-11800</v>
       </c>
       <c r="H33" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="J33" s="3">
         <v>-5600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-6200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-2400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-6900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-2600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-4100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1677,89 +1829,107 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-10000</v>
       </c>
-      <c r="E35" s="3">
-        <v>-19100</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-7200</v>
-      </c>
       <c r="G35" s="3">
-        <v>-7100</v>
+        <v>-11800</v>
       </c>
       <c r="H35" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="J35" s="3">
         <v>-5600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-6200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-2400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-6900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-2600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-4100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1774,8 +1944,10 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1790,63 +1962,71 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F41" s="3">
         <v>6000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>7600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>5400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>2300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>12600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>11400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>20900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>29000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>36300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>42500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>45900</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
         <v>100</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
@@ -1860,73 +2040,85 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F43" s="3">
         <v>3000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>100</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>300</v>
+      </c>
+      <c r="E44" s="3">
+        <v>200</v>
+      </c>
+      <c r="F44" s="3">
         <v>600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>100</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
@@ -1942,107 +2134,125 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>700</v>
+        <v>8400</v>
       </c>
       <c r="E45" s="3">
-        <v>1100</v>
+        <v>8400</v>
       </c>
       <c r="F45" s="3">
-        <v>1100</v>
+        <v>200</v>
       </c>
       <c r="G45" s="3">
-        <v>1600</v>
+        <v>200</v>
       </c>
       <c r="H45" s="3">
-        <v>1600</v>
-      </c>
-      <c r="I45" s="3">
-        <v>900</v>
-      </c>
-      <c r="J45" s="3">
-        <v>800</v>
+        <v>200</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K45" s="3">
         <v>900</v>
       </c>
       <c r="L45" s="3">
+        <v>800</v>
+      </c>
+      <c r="M45" s="3">
+        <v>900</v>
+      </c>
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>18400</v>
+      </c>
+      <c r="F46" s="3">
         <v>10300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>11600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>8400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>4800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>14400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>13700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>21700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>29900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>36800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>44400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>47700</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
+        <v>1600</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2056,63 +2266,75 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>53800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>54800</v>
+      </c>
+      <c r="F48" s="3">
         <v>74000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>72400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>69400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>38300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>33000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>30100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>28200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>19100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>16000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>12000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>4600</v>
+        <v>4500</v>
       </c>
       <c r="E49" s="3">
-        <v>4600</v>
+        <v>4500</v>
       </c>
       <c r="F49" s="3">
         <v>4600</v>
       </c>
       <c r="G49" s="3">
-        <v>3900</v>
+        <v>4600</v>
       </c>
       <c r="H49" s="3">
-        <v>3900</v>
+        <v>4600</v>
       </c>
       <c r="I49" s="3">
         <v>3900</v>
@@ -2124,16 +2346,22 @@
         <v>3900</v>
       </c>
       <c r="L49" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="M49" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="N49" s="3">
         <v>3800</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>3800</v>
+      </c>
+      <c r="P49" s="3">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2170,8 +2398,14 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2208,29 +2442,35 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>300</v>
-      </c>
-      <c r="E52" s="3">
-        <v>300</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1600</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3">
         <v>27700</v>
       </c>
-      <c r="H52" s="3">
-        <v>6100</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>4</v>
       </c>
@@ -2246,8 +2486,14 @@
       <c r="N52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2284,46 +2530,58 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>73800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>77700</v>
+      </c>
+      <c r="F54" s="3">
         <v>89300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>88900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>83900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>74700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>57400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>47600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>53800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>52900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>56600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>60200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>60200</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2338,8 +2596,10 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2354,69 +2614,77 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F57" s="3">
         <v>2900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>3900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2600</v>
       </c>
-      <c r="G57" s="3">
-        <v>7300</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J57" s="3">
         <v>3200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>6200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>3000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>4400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>10700</v>
+        <v>2600</v>
       </c>
       <c r="E58" s="3">
-        <v>16300</v>
+        <v>6500</v>
       </c>
       <c r="F58" s="3">
-        <v>17200</v>
+        <v>10800</v>
       </c>
       <c r="G58" s="3">
-        <v>6000</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>4</v>
+        <v>16400</v>
+      </c>
+      <c r="H58" s="3">
+        <v>17400</v>
+      </c>
+      <c r="I58" s="3">
+        <v>6100</v>
+      </c>
+      <c r="J58" s="3">
+        <v>100</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>4</v>
@@ -2430,84 +2698,102 @@
       <c r="N58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3300</v>
+        <v>1400</v>
       </c>
       <c r="E59" s="3">
-        <v>2100</v>
+        <v>2800</v>
       </c>
       <c r="F59" s="3">
-        <v>3200</v>
+        <v>2000</v>
       </c>
       <c r="G59" s="3">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="H59" s="3">
-        <v>100</v>
+        <v>2500</v>
       </c>
       <c r="I59" s="3">
-        <v>100</v>
-      </c>
-      <c r="J59" s="3">
-        <v>100</v>
+        <v>4400</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K59" s="3">
         <v>100</v>
       </c>
       <c r="L59" s="3">
+        <v>100</v>
+      </c>
+      <c r="M59" s="3">
+        <v>100</v>
+      </c>
+      <c r="N59" s="3">
         <v>300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>15800</v>
+      </c>
+      <c r="F60" s="3">
         <v>17000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>22300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>23000</v>
       </c>
-      <c r="G60" s="3">
-        <v>13400</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
+        <v>13700</v>
+      </c>
+      <c r="J60" s="3">
         <v>3300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>6300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>3100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>3700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>4700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2518,19 +2804,19 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>1700</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2544,46 +2830,58 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>400</v>
+      </c>
+      <c r="F62" s="3">
         <v>2200</v>
       </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
         <v>100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="L62" s="3">
         <v>100</v>
-      </c>
-      <c r="I62" s="3">
-        <v>100</v>
-      </c>
-      <c r="J62" s="3">
-        <v>100</v>
-      </c>
-      <c r="K62" s="3">
-        <v>200</v>
-      </c>
-      <c r="L62" s="3">
-        <v>200</v>
       </c>
       <c r="M62" s="3">
         <v>200</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="3">
+        <v>200</v>
+      </c>
+      <c r="O62" s="3">
+        <v>200</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2620,8 +2918,14 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2658,8 +2962,14 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2696,46 +3006,58 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>16200</v>
+      </c>
+      <c r="F66" s="3">
         <v>19200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>22300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>24700</v>
       </c>
-      <c r="G66" s="3">
-        <v>13400</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
+        <v>13800</v>
+      </c>
+      <c r="J66" s="3">
         <v>3400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>6500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>3200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>3900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>4900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2750,8 +3072,10 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2788,8 +3112,14 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2826,8 +3156,14 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2859,13 +3195,19 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
         <v>300</v>
       </c>
-      <c r="N70" s="3">
+      <c r="P70" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2902,46 +3244,58 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-225000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-213300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-189900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-176500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-167200</v>
       </c>
-      <c r="G72" s="3">
-        <v>-160000</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
+        <v>-160800</v>
+      </c>
+      <c r="J72" s="3">
         <v>-152900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-147300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-141100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-138600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-131800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-129200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-125100</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2978,8 +3332,14 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3016,8 +3376,14 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3054,46 +3420,58 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>59300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>61500</v>
+      </c>
+      <c r="F76" s="3">
         <v>70100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>66600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>59200</v>
       </c>
-      <c r="G76" s="3">
-        <v>61200</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
+        <v>60900</v>
+      </c>
+      <c r="J76" s="3">
         <v>53900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>45900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>47300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>49600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>52700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>55100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>57400</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3130,89 +3508,107 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-10000</v>
       </c>
-      <c r="E81" s="3">
-        <v>-19100</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-7200</v>
-      </c>
       <c r="G81" s="3">
-        <v>-7100</v>
+        <v>-11800</v>
       </c>
       <c r="H81" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="J81" s="3">
         <v>-5600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-6200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-2400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-6900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-2600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-4100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3227,19 +3623,21 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G83" s="3">
         <v>0</v>
@@ -3248,7 +3646,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J83" s="3">
         <v>0</v>
@@ -3265,8 +3663,14 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3303,8 +3707,14 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3341,8 +3751,14 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3379,8 +3795,14 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3417,8 +3839,14 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3455,46 +3883,58 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-5000</v>
       </c>
-      <c r="E89" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="H89" s="3">
         <v>-4800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-2600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-3400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-3300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-4000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-2900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-2900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-1700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3509,46 +3949,54 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-700</v>
       </c>
-      <c r="E91" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-6600</v>
-      </c>
       <c r="G91" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="I91" s="3">
         <v>-2900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-1700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-6100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-4100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-4100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-3800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-1600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3585,8 +4033,14 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3623,46 +4077,58 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-500</v>
       </c>
-      <c r="E94" s="3">
-        <v>-10900</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="H94" s="3">
         <v>-7300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-18700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-7800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-6100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-4100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-4100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-3800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-1600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3677,31 +4143,33 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3715,8 +4183,14 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3753,8 +4227,14 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3791,8 +4271,14 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3829,69 +4315,81 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F100" s="3">
         <v>3900</v>
       </c>
-      <c r="E100" s="3">
-        <v>23600</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
+        <v>8500</v>
+      </c>
+      <c r="H100" s="3">
         <v>15100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>11000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>12400</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>500</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>41200</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -3905,42 +4403,54 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1700</v>
       </c>
-      <c r="E102" s="3">
-        <v>5300</v>
-      </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H102" s="3">
         <v>3100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-10300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>1100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-9400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-8100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-7300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-6200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-3400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>33100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ABAT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ABAT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
   <si>
     <t>ABAT</t>
   </si>
@@ -656,92 +656,95 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>300</v>
+      </c>
+      <c r="E8" s="3">
         <v>200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>300</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G8" s="3" t="s">
         <v>4</v>
       </c>
@@ -754,8 +757,8 @@
       <c r="J8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -772,20 +775,23 @@
       <c r="P8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E9" s="3">
         <v>2500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3300</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G9" s="3" t="s">
         <v>4</v>
       </c>
@@ -816,20 +822,23 @@
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E10" s="3">
         <v>-2300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-3000</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G10" s="3" t="s">
         <v>4</v>
       </c>
@@ -860,8 +869,11 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,52 +890,56 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E12" s="3">
         <v>2000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>3200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>4000</v>
-      </c>
-      <c r="G12" s="3">
-        <v>5000</v>
       </c>
       <c r="H12" s="3">
         <v>3600</v>
       </c>
       <c r="I12" s="3">
+        <v>3600</v>
+      </c>
+      <c r="J12" s="3">
         <v>4100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1400</v>
-      </c>
-      <c r="N12" s="3">
-        <v>200</v>
       </c>
       <c r="O12" s="3">
         <v>200</v>
       </c>
       <c r="P12" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q12" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,20 +982,23 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3">
         <v>700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>10300</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
@@ -987,19 +1006,19 @@
         <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>-200</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1008,10 +1027,13 @@
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1019,11 +1041,11 @@
         <v>1300</v>
       </c>
       <c r="E15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F15" s="3">
         <v>1600</v>
       </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
       <c r="G15" s="3">
         <v>0</v>
       </c>
@@ -1054,8 +1076,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,96 +1094,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E17" s="3">
         <v>10000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>12400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8600</v>
       </c>
-      <c r="G17" s="3">
-        <v>10400</v>
-      </c>
       <c r="H17" s="3">
-        <v>8000</v>
+        <v>8800</v>
       </c>
       <c r="I17" s="3">
         <v>8000</v>
       </c>
       <c r="J17" s="3">
+        <v>8000</v>
+      </c>
+      <c r="K17" s="3">
         <v>5600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-9800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-12100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-8600</v>
       </c>
-      <c r="G18" s="3">
-        <v>-10400</v>
-      </c>
       <c r="H18" s="3">
-        <v>-8000</v>
+        <v>-8800</v>
       </c>
       <c r="I18" s="3">
         <v>-8000</v>
       </c>
       <c r="J18" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="K18" s="3">
         <v>-5600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,28 +1207,29 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-1100</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
-        <v>-500</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
+      <c r="H20" s="3">
+        <v>200</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -1205,71 +1238,77 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-8600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-10400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-8800</v>
       </c>
-      <c r="G21" s="3">
-        <v>-9900</v>
-      </c>
       <c r="H21" s="3">
-        <v>-8000</v>
+        <v>-9000</v>
       </c>
       <c r="I21" s="3">
         <v>-8000</v>
       </c>
       <c r="J21" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="K21" s="3">
         <v>-5600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-6200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-6800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-4100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
@@ -1281,22 +1320,22 @@
         <v>0</v>
       </c>
       <c r="H22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="J22" s="3">
+        <v>100</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1307,52 +1346,58 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-11700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-23400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10000</v>
       </c>
-      <c r="G23" s="3">
-        <v>-11800</v>
-      </c>
       <c r="H23" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="I23" s="3">
         <v>-8900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-8000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-6200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1377,8 +1422,8 @@
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1395,8 +1440,11 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1487,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-11700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-23400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10000</v>
       </c>
-      <c r="G26" s="3">
-        <v>-11800</v>
-      </c>
       <c r="H26" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="I26" s="3">
         <v>-8900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-8000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-6200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-6900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-11800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-23400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10000</v>
       </c>
-      <c r="G27" s="3">
-        <v>-11800</v>
-      </c>
       <c r="H27" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="I27" s="3">
         <v>-8900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-8000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-5600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-6200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-6900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1628,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1675,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1722,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,28 +1769,31 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
-        <v>500</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
+      <c r="H32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -1733,66 +1802,72 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-11700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-23400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10000</v>
       </c>
-      <c r="G33" s="3">
-        <v>-11800</v>
-      </c>
       <c r="H33" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="I33" s="3">
         <v>-8900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-8000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-6200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-6900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +1910,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-11700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-23400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10000</v>
       </c>
-      <c r="G35" s="3">
-        <v>-11800</v>
-      </c>
       <c r="H35" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="I35" s="3">
         <v>-8900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-8000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-6200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-6900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2030,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,52 +2049,56 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E41" s="3">
         <v>5800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>12600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>20900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>29000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>36300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>42500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>45900</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2020,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
         <v>100</v>
@@ -2029,7 +2118,7 @@
         <v>100</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -2046,14 +2135,17 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>4</v>
+      <c r="O42" s="3">
+        <v>0</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2061,32 +2153,32 @@
         <v>400</v>
       </c>
       <c r="E43" s="3">
+        <v>400</v>
+      </c>
+      <c r="F43" s="3">
         <v>1000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>100</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2096,32 +2188,35 @@
       <c r="P43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>600</v>
+      </c>
+      <c r="E44" s="3">
         <v>300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>200</v>
-      </c>
-      <c r="F44" s="3">
-        <v>600</v>
       </c>
       <c r="G44" s="3">
         <v>600</v>
       </c>
       <c r="H44" s="3">
+        <v>600</v>
+      </c>
+      <c r="I44" s="3">
         <v>400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>100</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
@@ -2140,8 +2235,11 @@
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2152,7 +2250,7 @@
         <v>8400</v>
       </c>
       <c r="F45" s="3">
-        <v>200</v>
+        <v>8400</v>
       </c>
       <c r="G45" s="3">
         <v>200</v>
@@ -2160,76 +2258,82 @@
       <c r="H45" s="3">
         <v>200</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
+      <c r="I45" s="3">
+        <v>200</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3">
         <v>900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>400</v>
-      </c>
-      <c r="O45" s="3">
-        <v>1800</v>
       </c>
       <c r="P45" s="3">
         <v>1800</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E46" s="3">
         <v>15500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>14400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>13700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>21700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>29900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>36800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>44400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>47700</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2239,24 +2343,24 @@
       <c r="E47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F47" s="3">
-        <v>300</v>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G47" s="3">
         <v>300</v>
       </c>
       <c r="H47" s="3">
+        <v>300</v>
+      </c>
+      <c r="I47" s="3">
         <v>1600</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K47" s="3">
         <v>6100</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -2272,52 +2376,58 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>53300</v>
+      </c>
+      <c r="E48" s="3">
         <v>53800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>54800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>74000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>72400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>69400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>38300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>33000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>30100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>28200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>19100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>16000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2328,7 +2438,7 @@
         <v>4500</v>
       </c>
       <c r="F49" s="3">
-        <v>4600</v>
+        <v>4500</v>
       </c>
       <c r="G49" s="3">
         <v>4600</v>
@@ -2337,7 +2447,7 @@
         <v>4600</v>
       </c>
       <c r="I49" s="3">
-        <v>3900</v>
+        <v>4600</v>
       </c>
       <c r="J49" s="3">
         <v>3900</v>
@@ -2352,7 +2462,7 @@
         <v>3900</v>
       </c>
       <c r="N49" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="O49" s="3">
         <v>3800</v>
@@ -2360,8 +2470,11 @@
       <c r="P49" s="3">
         <v>3800</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2517,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,8 +2564,11 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2468,12 +2587,12 @@
       <c r="H52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I52" s="3">
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3">
         <v>27700</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>4</v>
       </c>
@@ -2492,8 +2611,11 @@
       <c r="P52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2658,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>88300</v>
+      </c>
+      <c r="E54" s="3">
         <v>73800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>77700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>89300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>88900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>83900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>74700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>57400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>47600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>53800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>52900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>56600</v>
-      </c>
-      <c r="O54" s="3">
-        <v>60200</v>
       </c>
       <c r="P54" s="3">
         <v>60200</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3">
+        <v>60200</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2726,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,79 +2745,83 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E58" s="3">
         <v>2600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>16400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>17400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>100</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>4</v>
       </c>
@@ -2704,34 +2837,37 @@
       <c r="P58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>200</v>
+      </c>
+      <c r="E59" s="3">
         <v>1400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4400</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K59" s="3">
-        <v>100</v>
+      <c r="K59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L59" s="3">
         <v>100</v>
@@ -2740,65 +2876,71 @@
         <v>100</v>
       </c>
       <c r="N59" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="O59" s="3">
         <v>300</v>
       </c>
       <c r="P59" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E60" s="3">
         <v>10000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>15800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>17000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>22300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>23000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
@@ -2810,16 +2952,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>1700</v>
-      </c>
-      <c r="I61" s="3">
-        <v>100</v>
       </c>
       <c r="J61" s="3">
         <v>100</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -2836,25 +2978,28 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3">
         <v>4500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2200</v>
       </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>4</v>
+      <c r="H62" s="3">
+        <v>0</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>4</v>
@@ -2862,14 +3007,14 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
-        <v>100</v>
+      <c r="K62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L62" s="3">
         <v>100</v>
       </c>
       <c r="M62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N62" s="3">
         <v>200</v>
@@ -2877,11 +3022,14 @@
       <c r="O62" s="3">
         <v>200</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3072,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3119,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,52 +3166,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E66" s="3">
         <v>14500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>16200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>19200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>22300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>24700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3234,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3279,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3326,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3201,13 +3368,16 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
         <v>300</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,52 +3420,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-238400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-225000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-213300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-189900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-176500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-167200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-160800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-152900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-147300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-141100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-138600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-131800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-129200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-125100</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3514,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3561,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3608,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>70600</v>
+      </c>
+      <c r="E76" s="3">
         <v>59300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>61500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>70100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>66600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>59200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>60900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>53900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>45900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>47300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>49600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>52700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>55100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>57400</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +3702,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-11700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-23400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10000</v>
       </c>
-      <c r="G81" s="3">
-        <v>-11800</v>
-      </c>
       <c r="H81" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="I81" s="3">
         <v>-8900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-8000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-6200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-6900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,8 +3822,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3640,17 +3838,17 @@
         <v>100</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
         <v>0</v>
       </c>
       <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
         <v>100</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
       <c r="K83" s="3">
         <v>0</v>
       </c>
@@ -3669,8 +3867,11 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +3914,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +3961,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4008,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4055,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4102,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-5600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4000</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-2900</v>
       </c>
       <c r="N89" s="3">
         <v>-2900</v>
       </c>
       <c r="O89" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="P89" s="3">
         <v>-1700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,52 +4170,56 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-700</v>
       </c>
-      <c r="G91" s="3">
-        <v>-4600</v>
-      </c>
       <c r="H91" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="I91" s="3">
         <v>-6500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6100</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-4100</v>
       </c>
       <c r="M91" s="3">
         <v>-4100</v>
       </c>
       <c r="N91" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="O91" s="3">
         <v>-3800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4262,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,52 +4309,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-18700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6100</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-4100</v>
       </c>
       <c r="M94" s="3">
         <v>-4100</v>
       </c>
       <c r="N94" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="O94" s="3">
         <v>-3800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4377,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4171,8 +4404,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -4189,8 +4422,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4469,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4516,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,52 +4563,58 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E100" s="3">
         <v>5200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>8500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>15100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>11000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>12400</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>500</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>41200</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4391,8 +4639,8 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4409,48 +4657,54 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-10300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-9400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-8100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-7300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-6200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>33100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ABAT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ABAT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
   <si>
     <t>ABAT</t>
   </si>
@@ -656,98 +656,102 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E8" s="3">
         <v>300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>300</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H8" s="3" t="s">
         <v>4</v>
       </c>
@@ -760,8 +764,8 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -778,23 +782,26 @@
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E9" s="3">
         <v>3300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3300</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H9" s="3" t="s">
         <v>4</v>
       </c>
@@ -825,23 +832,26 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E10" s="3">
         <v>-3000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-2300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-3000</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H10" s="3" t="s">
         <v>4</v>
       </c>
@@ -872,8 +882,11 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -891,55 +904,59 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E12" s="3">
         <v>2900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>4000</v>
-      </c>
-      <c r="H12" s="3">
-        <v>3600</v>
       </c>
       <c r="I12" s="3">
         <v>3600</v>
       </c>
       <c r="J12" s="3">
+        <v>3600</v>
+      </c>
+      <c r="K12" s="3">
         <v>4100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1400</v>
-      </c>
-      <c r="O12" s="3">
-        <v>200</v>
       </c>
       <c r="P12" s="3">
         <v>200</v>
       </c>
       <c r="Q12" s="3">
+        <v>200</v>
+      </c>
+      <c r="R12" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -985,23 +1002,26 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
         <v>700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>10300</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
@@ -1009,19 +1029,19 @@
         <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>-200</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1030,25 +1050,28 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="E15" s="3">
         <v>1300</v>
       </c>
       <c r="F15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G15" s="3">
         <v>1600</v>
       </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
       <c r="H15" s="3">
         <v>0</v>
       </c>
@@ -1079,8 +1102,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1095,102 +1121,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E17" s="3">
         <v>14100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>12400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8800</v>
-      </c>
-      <c r="I17" s="3">
-        <v>8000</v>
       </c>
       <c r="J17" s="3">
         <v>8000</v>
       </c>
       <c r="K17" s="3">
+        <v>8000</v>
+      </c>
+      <c r="L17" s="3">
         <v>5600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-13800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-9800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-12100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-8600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-8800</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-8000</v>
       </c>
       <c r="J18" s="3">
         <v>-8000</v>
       </c>
       <c r="K18" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="L18" s="3">
         <v>-5600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-6200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1208,31 +1241,32 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>200</v>
       </c>
       <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="I20" s="3">
+        <v>200</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1241,77 +1275,83 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-11400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-8600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-10400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-8800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-9000</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-8000</v>
       </c>
       <c r="J21" s="3">
         <v>-8000</v>
       </c>
       <c r="K21" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="L21" s="3">
         <v>-5600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-6200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-6800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -1323,22 +1363,22 @@
         <v>0</v>
       </c>
       <c r="I22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="K22" s="3">
+        <v>100</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1349,55 +1389,61 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-13400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-11700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-23400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-10200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-8900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-8000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1425,8 +1471,8 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1443,8 +1489,11 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1490,102 +1539,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-13400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-11700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-23400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-10200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-8900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-8000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-6900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-13400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-11800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-23400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-10200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-8900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-8000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-6900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1631,8 +1689,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1678,8 +1739,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1725,8 +1789,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1772,31 +1839,34 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>1100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-200</v>
       </c>
       <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="I32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -1805,69 +1875,75 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-13400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-11700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-23400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-10200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-8900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-8000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-6900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1913,107 +1989,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-13400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-11700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-23400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-10200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-8900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-8000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-6900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2031,8 +2116,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2050,55 +2136,59 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E41" s="3">
         <v>15600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>12600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>20900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>29000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>36300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>42500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>45900</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2112,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
         <v>100</v>
@@ -2121,7 +2211,7 @@
         <v>100</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2138,50 +2228,53 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>4</v>
+      <c r="P42" s="3">
+        <v>0</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="E43" s="3">
         <v>400</v>
       </c>
       <c r="F43" s="3">
+        <v>400</v>
+      </c>
+      <c r="G43" s="3">
         <v>1000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>100</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2191,35 +2284,38 @@
       <c r="Q43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>300</v>
+      </c>
+      <c r="E44" s="3">
         <v>600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>200</v>
-      </c>
-      <c r="G44" s="3">
-        <v>600</v>
       </c>
       <c r="H44" s="3">
         <v>600</v>
       </c>
       <c r="I44" s="3">
+        <v>600</v>
+      </c>
+      <c r="J44" s="3">
         <v>400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>100</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
@@ -2238,13 +2334,16 @@
       <c r="Q44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>8400</v>
+        <v>12200</v>
       </c>
       <c r="E45" s="3">
         <v>8400</v>
@@ -2253,7 +2352,7 @@
         <v>8400</v>
       </c>
       <c r="G45" s="3">
-        <v>200</v>
+        <v>8400</v>
       </c>
       <c r="H45" s="3">
         <v>200</v>
@@ -2261,79 +2360,85 @@
       <c r="I45" s="3">
         <v>200</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>4</v>
+      <c r="J45" s="3">
+        <v>200</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3">
         <v>900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>400</v>
-      </c>
-      <c r="P45" s="3">
-        <v>1800</v>
       </c>
       <c r="Q45" s="3">
         <v>1800</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E46" s="3">
         <v>30500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>15500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>18400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>14400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>13700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>21700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>29900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>36800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>44400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>47700</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2346,24 +2451,24 @@
       <c r="F47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G47" s="3">
-        <v>300</v>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H47" s="3">
         <v>300</v>
       </c>
       <c r="I47" s="3">
+        <v>300</v>
+      </c>
+      <c r="J47" s="3">
         <v>1600</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L47" s="3">
         <v>6100</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -2379,60 +2484,66 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>52400</v>
+      </c>
+      <c r="E48" s="3">
         <v>53300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>53800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>54800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>74000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>72400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>69400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>38300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>33000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>30100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>28200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>19100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>16000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>4500</v>
+        <v>800</v>
       </c>
       <c r="E49" s="3">
         <v>4500</v>
@@ -2441,7 +2552,7 @@
         <v>4500</v>
       </c>
       <c r="G49" s="3">
-        <v>4600</v>
+        <v>4500</v>
       </c>
       <c r="H49" s="3">
         <v>4600</v>
@@ -2450,7 +2561,7 @@
         <v>4600</v>
       </c>
       <c r="J49" s="3">
-        <v>3900</v>
+        <v>4600</v>
       </c>
       <c r="K49" s="3">
         <v>3900</v>
@@ -2465,7 +2576,7 @@
         <v>3900</v>
       </c>
       <c r="O49" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="P49" s="3">
         <v>3800</v>
@@ -2473,8 +2584,11 @@
       <c r="Q49" s="3">
         <v>3800</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2520,8 +2634,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2567,8 +2684,11 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2590,12 +2710,12 @@
       <c r="I52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K52" s="3">
         <v>27700</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>4</v>
       </c>
@@ -2614,8 +2734,11 @@
       <c r="Q52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2661,55 +2784,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>76500</v>
+      </c>
+      <c r="E54" s="3">
         <v>88300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>73800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>77700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>89300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>88900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>83900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>74700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>57400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>47600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>53800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>52900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>56600</v>
-      </c>
-      <c r="P54" s="3">
-        <v>60200</v>
       </c>
       <c r="Q54" s="3">
         <v>60200</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3">
+        <v>60200</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2727,8 +2856,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2746,85 +2876,89 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E57" s="3">
         <v>2000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E58" s="3">
         <v>10300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>10800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>16400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>17400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>100</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>4</v>
       </c>
@@ -2840,37 +2974,40 @@
       <c r="Q58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3">
         <v>200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4400</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L59" s="3">
-        <v>100</v>
+      <c r="L59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M59" s="3">
         <v>100</v>
@@ -2879,72 +3016,78 @@
         <v>100</v>
       </c>
       <c r="O59" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="P59" s="3">
         <v>300</v>
       </c>
       <c r="Q59" s="3">
+        <v>300</v>
+      </c>
+      <c r="R59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E60" s="3">
         <v>17400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>17000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>22300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>23000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>13700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>200</v>
+      </c>
+      <c r="E61" s="3">
         <v>300</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
@@ -2955,16 +3098,16 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>1700</v>
-      </c>
-      <c r="J61" s="3">
-        <v>100</v>
       </c>
       <c r="K61" s="3">
         <v>100</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -2981,28 +3124,31 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E62" s="3">
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3">
         <v>4500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2200</v>
       </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
+      <c r="I62" s="3">
+        <v>0</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>4</v>
@@ -3010,14 +3156,14 @@
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="3">
-        <v>100</v>
+      <c r="L62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M62" s="3">
         <v>100</v>
       </c>
       <c r="N62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O62" s="3">
         <v>200</v>
@@ -3025,11 +3171,14 @@
       <c r="P62" s="3">
         <v>200</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>200</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3075,8 +3224,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3122,8 +3274,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3169,55 +3324,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E66" s="3">
         <v>17700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>19200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>22300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>24700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3235,8 +3396,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3282,8 +3444,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3329,8 +3494,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3371,13 +3539,16 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>300</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3423,55 +3594,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-249900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-238400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-225000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-213300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-189900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-176500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-167200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-160800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-152900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-147300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-141100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-138600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-131800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-129200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-125100</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3517,8 +3694,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3564,8 +3744,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3611,55 +3794,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>65600</v>
+      </c>
+      <c r="E76" s="3">
         <v>70600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>59300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>61500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>70100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>66600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>59200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>60900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>53900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>45900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>47300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>49600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>52700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>55100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>57400</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3705,107 +3894,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-13400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-11700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-23400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-10200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-8900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-8000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-6900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3823,8 +4021,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3841,17 +4040,17 @@
         <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I83" s="3">
         <v>0</v>
       </c>
       <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3">
         <v>100</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
@@ -3870,8 +4069,11 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3917,8 +4119,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3964,8 +4169,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4011,8 +4219,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4058,8 +4269,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4105,55 +4319,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4000</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-2900</v>
       </c>
       <c r="O89" s="3">
         <v>-2900</v>
       </c>
       <c r="P89" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4171,55 +4391,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6100</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-4100</v>
       </c>
       <c r="N91" s="3">
         <v>-4100</v>
       </c>
       <c r="O91" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="P91" s="3">
         <v>-3800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4265,8 +4489,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4312,55 +4539,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-18700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6100</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-4100</v>
       </c>
       <c r="N94" s="3">
         <v>-4100</v>
       </c>
       <c r="O94" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="P94" s="3">
         <v>-3800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4378,8 +4611,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4407,8 +4641,8 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4425,8 +4659,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4472,8 +4709,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4519,8 +4759,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4566,55 +4809,61 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E100" s="3">
         <v>22800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>8500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>15100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>11000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>12400</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>-300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>500</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>41200</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4642,8 +4891,8 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4660,51 +4909,57 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="E102" s="3">
         <v>14900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-10300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-9400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-8100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-7300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>33100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ABAT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ABAT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
   <si>
     <t>ABAT</t>
   </si>
@@ -2883,7 +2883,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3800</v>
+        <v>700</v>
       </c>
       <c r="E57" s="3">
         <v>2000</v>
@@ -2982,8 +2982,8 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>4</v>
+      <c r="D59" s="3">
+        <v>100</v>
       </c>
       <c r="E59" s="3">
         <v>200</v>
@@ -4410,7 +4410,7 @@
         <v>-200</v>
       </c>
       <c r="H91" s="3">
-        <v>-700</v>
+        <v>-1300</v>
       </c>
       <c r="I91" s="3">
         <v>-3900</v>

--- a/AAII_Financials/Quarterly/ABAT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ABAT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="92">
   <si>
     <t>ABAT</t>
   </si>
@@ -656,119 +656,122 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E8" s="3">
         <v>900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>300</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
@@ -781,8 +784,8 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
@@ -799,32 +802,35 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E9" s="3">
         <v>4500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3300</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
@@ -855,32 +861,35 @@
       <c r="T9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E10" s="3">
         <v>-3500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-2600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-2700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-3000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-2300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-3000</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
@@ -911,8 +920,11 @@
       <c r="T10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,64 +945,68 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E12" s="3">
         <v>2700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4000</v>
-      </c>
-      <c r="K12" s="3">
-        <v>3600</v>
       </c>
       <c r="L12" s="3">
         <v>3600</v>
       </c>
       <c r="M12" s="3">
+        <v>3600</v>
+      </c>
+      <c r="N12" s="3">
         <v>4100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1400</v>
-      </c>
-      <c r="R12" s="3">
-        <v>200</v>
       </c>
       <c r="S12" s="3">
         <v>200</v>
       </c>
       <c r="T12" s="3">
+        <v>200</v>
+      </c>
+      <c r="U12" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,32 +1061,35 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
         <v>1400</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
         <v>700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>10300</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
@@ -1078,19 +1097,19 @@
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-200</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1099,34 +1118,37 @@
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="E15" s="3">
         <v>1300</v>
       </c>
       <c r="F15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G15" s="3">
         <v>1200</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1300</v>
       </c>
       <c r="H15" s="3">
         <v>1300</v>
       </c>
       <c r="I15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J15" s="3">
         <v>1600</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
@@ -1157,8 +1179,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1201,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E17" s="3">
         <v>11100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>11600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>10000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8800</v>
-      </c>
-      <c r="L17" s="3">
-        <v>8000</v>
       </c>
       <c r="M17" s="3">
         <v>8000</v>
       </c>
       <c r="N17" s="3">
+        <v>8000</v>
+      </c>
+      <c r="O17" s="3">
         <v>5600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-10100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-7800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-10600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-13800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-9800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-12100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8800</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-8000</v>
       </c>
       <c r="M18" s="3">
         <v>-8000</v>
       </c>
       <c r="N18" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="O18" s="3">
         <v>-5600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-6200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-6800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-4100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,40 +1342,41 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-1100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>200</v>
       </c>
       <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="L20" s="3">
+        <v>200</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1352,83 +1385,89 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-8700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-6500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-9400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-11400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-8600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-10400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-8800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-9000</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-8000</v>
       </c>
       <c r="M21" s="3">
         <v>-8000</v>
       </c>
       <c r="N21" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="O21" s="3">
         <v>-5600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-6200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-6800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-4100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
@@ -1436,11 +1475,11 @@
       <c r="F22" s="3">
         <v>0</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
@@ -1452,22 +1491,22 @@
         <v>0</v>
       </c>
       <c r="L22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="N22" s="3">
+        <v>100</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1478,64 +1517,70 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-10300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-10200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-11500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-13400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-11700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-23400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-10000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-10200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-8900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-8000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1572,8 +1617,8 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -1590,8 +1635,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1694,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-10300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-10200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-11500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-13400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-11700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-23400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-10000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-10200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-8900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-8000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-6200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-6900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-10300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-10200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-11500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-13400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-11800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-23400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-10000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-10200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-8900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-8000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-6200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-6900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1871,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1930,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1989,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,40 +2048,43 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>300</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>1100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-200</v>
       </c>
       <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="L32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -2024,78 +2093,84 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-10300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-10200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-11500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-13400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-11700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-23400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-10000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-10200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-8900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-8000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-6200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-6900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2225,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-10300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-10200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-11500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-13400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-11700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-23400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-10000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-10200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-8900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-8000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-6200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-6900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2373,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,64 +2396,68 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>47900</v>
+      </c>
+      <c r="E41" s="3">
         <v>30100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>15600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>12600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>20900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>29000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>36300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>42500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>45900</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2391,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>100</v>
@@ -2400,7 +2489,7 @@
         <v>100</v>
       </c>
       <c r="M42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -2417,59 +2506,62 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>4</v>
+      <c r="S42" s="3">
+        <v>0</v>
       </c>
       <c r="T42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E43" s="3">
         <v>1700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1200</v>
-      </c>
-      <c r="G43" s="3">
-        <v>400</v>
       </c>
       <c r="H43" s="3">
         <v>400</v>
       </c>
       <c r="I43" s="3">
+        <v>400</v>
+      </c>
+      <c r="J43" s="3">
         <v>1000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>100</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2479,44 +2571,47 @@
       <c r="T43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>300</v>
+      </c>
+      <c r="E44" s="3">
         <v>100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>200</v>
-      </c>
-      <c r="J44" s="3">
-        <v>600</v>
       </c>
       <c r="K44" s="3">
         <v>600</v>
       </c>
       <c r="L44" s="3">
+        <v>600</v>
+      </c>
+      <c r="M44" s="3">
         <v>400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>100</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
@@ -2535,8 +2630,11 @@
       <c r="T44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2544,13 +2642,13 @@
         <v>3800</v>
       </c>
       <c r="E45" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F45" s="3">
         <v>9800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12200</v>
-      </c>
-      <c r="G45" s="3">
-        <v>8400</v>
       </c>
       <c r="H45" s="3">
         <v>8400</v>
@@ -2559,7 +2657,7 @@
         <v>8400</v>
       </c>
       <c r="J45" s="3">
-        <v>200</v>
+        <v>8400</v>
       </c>
       <c r="K45" s="3">
         <v>200</v>
@@ -2567,88 +2665,94 @@
       <c r="L45" s="3">
         <v>200</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>4</v>
+      <c r="M45" s="3">
+        <v>200</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P45" s="3">
         <v>900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>400</v>
-      </c>
-      <c r="S45" s="3">
-        <v>1800</v>
       </c>
       <c r="T45" s="3">
         <v>1800</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>63100</v>
+      </c>
+      <c r="E46" s="3">
         <v>41500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>29500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>23300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>30500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>15500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>18400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>14400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>13700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>21700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>29900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>36800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>44400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>47700</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2670,24 +2774,24 @@
       <c r="I47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J47" s="3">
-        <v>300</v>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
         <v>300</v>
       </c>
       <c r="L47" s="3">
+        <v>300</v>
+      </c>
+      <c r="M47" s="3">
         <v>1600</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O47" s="3">
         <v>6100</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
@@ -2703,64 +2807,70 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>59500</v>
+      </c>
+      <c r="E48" s="3">
         <v>59200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>54200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>52400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>53300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>53800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>54800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>74000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>72400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>69400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>38300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>33000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>30100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>28200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>19100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>16000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>12000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2774,7 +2884,7 @@
         <v>800</v>
       </c>
       <c r="G49" s="3">
-        <v>4500</v>
+        <v>800</v>
       </c>
       <c r="H49" s="3">
         <v>4500</v>
@@ -2783,7 +2893,7 @@
         <v>4500</v>
       </c>
       <c r="J49" s="3">
-        <v>4600</v>
+        <v>4500</v>
       </c>
       <c r="K49" s="3">
         <v>4600</v>
@@ -2792,7 +2902,7 @@
         <v>4600</v>
       </c>
       <c r="M49" s="3">
-        <v>3900</v>
+        <v>4600</v>
       </c>
       <c r="N49" s="3">
         <v>3900</v>
@@ -2807,7 +2917,7 @@
         <v>3900</v>
       </c>
       <c r="R49" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="S49" s="3">
         <v>3800</v>
@@ -2815,8 +2925,11 @@
       <c r="T49" s="3">
         <v>3800</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2984,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,8 +3043,11 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2959,12 +3078,12 @@
       <c r="L52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N52" s="3">
         <v>27700</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>4</v>
       </c>
@@ -2983,8 +3102,11 @@
       <c r="T52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,64 +3161,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>123300</v>
+      </c>
+      <c r="E54" s="3">
         <v>101500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>84500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>76500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>88300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>73800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>77700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>89300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>88900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>83900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>74700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>57400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>47600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>53800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>52900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>56600</v>
-      </c>
-      <c r="S54" s="3">
-        <v>60200</v>
       </c>
       <c r="T54" s="3">
         <v>60200</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3">
+        <v>60200</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3245,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,64 +3268,68 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>400</v>
+      </c>
+      <c r="E57" s="3">
         <v>300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3204,38 +3337,38 @@
         <v>100</v>
       </c>
       <c r="E58" s="3">
+        <v>100</v>
+      </c>
+      <c r="F58" s="3">
         <v>7800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>10300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>16400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>17400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>100</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>4</v>
       </c>
@@ -3251,46 +3384,49 @@
       <c r="T58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E59" s="3">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3">
         <v>300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4400</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O59" s="3">
-        <v>100</v>
+      <c r="O59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P59" s="3">
         <v>100</v>
@@ -3299,77 +3435,83 @@
         <v>100</v>
       </c>
       <c r="R59" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="S59" s="3">
         <v>300</v>
       </c>
       <c r="T59" s="3">
+        <v>300</v>
+      </c>
+      <c r="U59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E60" s="3">
         <v>5300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>13700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>17400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>15800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>17000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>22300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>23000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>13700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
         <v>200</v>
@@ -3378,11 +3520,11 @@
         <v>200</v>
       </c>
       <c r="G61" s="3">
+        <v>200</v>
+      </c>
+      <c r="H61" s="3">
         <v>300</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -3393,16 +3535,16 @@
         <v>0</v>
       </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>1700</v>
-      </c>
-      <c r="M61" s="3">
-        <v>100</v>
       </c>
       <c r="N61" s="3">
         <v>100</v>
       </c>
       <c r="O61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P61" s="3">
         <v>0</v>
@@ -3419,8 +3561,11 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3436,20 +3581,20 @@
       <c r="G62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3">
         <v>4500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2200</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>4</v>
+      <c r="L62" s="3">
+        <v>0</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>4</v>
@@ -3457,14 +3602,14 @@
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O62" s="3">
-        <v>100</v>
+      <c r="O62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P62" s="3">
         <v>100</v>
       </c>
       <c r="Q62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R62" s="3">
         <v>200</v>
@@ -3472,11 +3617,14 @@
       <c r="S62" s="3">
         <v>200</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T62" s="3">
+        <v>200</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3679,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3738,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,64 +3797,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E66" s="3">
         <v>5500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>13900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>17700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>16200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>19200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>22300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>24700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3881,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3938,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3997,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3884,13 +4051,16 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>300</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,64 +4115,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-279700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-270400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-260100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-249900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-238400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-225000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-213300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-189900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-176500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-167200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-160800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-152900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-147300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-141100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-138600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-131800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-129200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-125100</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4233,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4292,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,64 +4351,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>119000</v>
+      </c>
+      <c r="E76" s="3">
         <v>96000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>70600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>65600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>70600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>59300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>61500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>70100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>66600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>59200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>60900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>53900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>45900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>47300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>49600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>52700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>55100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>57400</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4469,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-10300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-10200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-11500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-13400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-11700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-23400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-10000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-10200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-8900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-8000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-6200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-6900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,8 +4617,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4429,10 +4627,10 @@
         <v>1300</v>
       </c>
       <c r="E83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F83" s="3">
         <v>1600</v>
-      </c>
-      <c r="F83" s="3">
-        <v>100</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>
@@ -4447,17 +4645,17 @@
         <v>100</v>
       </c>
       <c r="K83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
       <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
         <v>100</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
       <c r="O83" s="3">
         <v>0</v>
       </c>
@@ -4476,8 +4674,11 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4733,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4792,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4851,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4910,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4969,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-10300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-4000</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-2900</v>
       </c>
       <c r="R89" s="3">
         <v>-2900</v>
       </c>
       <c r="S89" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="T89" s="3">
         <v>-1700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,64 +5053,68 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-700</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-500</v>
       </c>
       <c r="F91" s="3">
         <v>-500</v>
       </c>
       <c r="G91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H91" s="3">
         <v>-600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6100</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-4100</v>
       </c>
       <c r="Q91" s="3">
         <v>-4100</v>
       </c>
       <c r="R91" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="S91" s="3">
         <v>-3800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5169,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,64 +5228,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-700</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-500</v>
       </c>
       <c r="F94" s="3">
         <v>-500</v>
       </c>
       <c r="G94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H94" s="3">
         <v>-600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-18700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6100</v>
-      </c>
-      <c r="P94" s="3">
-        <v>-4100</v>
       </c>
       <c r="Q94" s="3">
         <v>-4100</v>
       </c>
       <c r="R94" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="S94" s="3">
         <v>-3800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5312,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5118,8 +5351,8 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -5136,8 +5369,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5428,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5487,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,64 +5546,70 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E100" s="3">
         <v>26300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>11000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>22800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>5200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>6900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>8500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>15100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>11000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>12400</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>-300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>500</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>41200</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5398,8 +5646,8 @@
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -5416,60 +5664,66 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E102" s="3">
         <v>18400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-12800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>14900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-10300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-9400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-7300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-6200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>33100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ABAT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ABAT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="92">
   <si>
     <t>ABAT</t>
   </si>
@@ -656,125 +656,129 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E8" s="3">
         <v>4800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>300</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
@@ -787,8 +791,8 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -805,35 +809,38 @@
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E9" s="3">
         <v>6400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3300</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
@@ -864,35 +871,38 @@
       <c r="U9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>700</v>
+      </c>
+      <c r="E10" s="3">
         <v>-1600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-3500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-2600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-2700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-3000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-2300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-3000</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
@@ -923,8 +933,11 @@
       <c r="U10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -946,67 +959,71 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E12" s="3">
         <v>3800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4000</v>
-      </c>
-      <c r="L12" s="3">
-        <v>3600</v>
       </c>
       <c r="M12" s="3">
         <v>3600</v>
       </c>
       <c r="N12" s="3">
+        <v>3600</v>
+      </c>
+      <c r="O12" s="3">
         <v>4100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1400</v>
-      </c>
-      <c r="S12" s="3">
-        <v>200</v>
       </c>
       <c r="T12" s="3">
         <v>200</v>
       </c>
       <c r="U12" s="3">
+        <v>200</v>
+      </c>
+      <c r="V12" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1064,8 +1081,11 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1075,24 +1095,24 @@
       <c r="E14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3">
         <v>1400</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
         <v>700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>10300</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1100,19 +1120,19 @@
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-200</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1121,10 +1141,13 @@
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1132,26 +1155,26 @@
         <v>1500</v>
       </c>
       <c r="E15" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="F15" s="3">
         <v>1300</v>
       </c>
       <c r="G15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H15" s="3">
         <v>1200</v>
-      </c>
-      <c r="H15" s="3">
-        <v>1300</v>
       </c>
       <c r="I15" s="3">
         <v>1300</v>
       </c>
       <c r="J15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K15" s="3">
         <v>1600</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1182,8 +1205,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1202,126 +1228,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>42200</v>
+      </c>
+      <c r="E17" s="3">
         <v>14600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>11100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>14100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>10000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8800</v>
-      </c>
-      <c r="M17" s="3">
-        <v>8000</v>
       </c>
       <c r="N17" s="3">
         <v>8000</v>
       </c>
       <c r="O17" s="3">
+        <v>8000</v>
+      </c>
+      <c r="P17" s="3">
         <v>5600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-34400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-9900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-10100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-7800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-10600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-13800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-9800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-12100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8800</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-8000</v>
       </c>
       <c r="N18" s="3">
         <v>-8000</v>
       </c>
       <c r="O18" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="P18" s="3">
         <v>-5600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-6800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-4100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1343,43 +1376,44 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-1100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-100</v>
-      </c>
-      <c r="K20" s="3">
-        <v>200</v>
       </c>
       <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
+      <c r="M20" s="3">
+        <v>200</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O20" s="3">
         <v>0</v>
@@ -1388,89 +1422,95 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-32600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-8100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-8700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-6500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-9400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-11400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-8600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-10400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-8800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-9000</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-8000</v>
       </c>
       <c r="N21" s="3">
         <v>-8000</v>
       </c>
       <c r="O21" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="P21" s="3">
         <v>-5600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-6800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-4100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -1478,11 +1518,11 @@
       <c r="G22" s="3">
         <v>0</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -1494,22 +1534,22 @@
         <v>0</v>
       </c>
       <c r="M22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="O22" s="3">
+        <v>100</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1520,67 +1560,73 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-33800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-9300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-10300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-11500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-13400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-11700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-23400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-10000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-10200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-8900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-8000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1620,8 +1666,8 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1638,8 +1684,11 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1697,126 +1746,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-33800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-10300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-11500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-13400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-11700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-23400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-10000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-10200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-8900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-8000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-6900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-33800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-10300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-11500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-13400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-11800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-23400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-10000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-10200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-8900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-8000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-6900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1874,8 +1932,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1933,8 +1994,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1992,8 +2056,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2051,43 +2118,46 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>200</v>
+      </c>
+      <c r="E32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>1100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>100</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-200</v>
       </c>
       <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
+      <c r="M32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
@@ -2096,81 +2166,87 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-33800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-9300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-10300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-11500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-13400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-11700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-23400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-10000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-10200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-8900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-8000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-6900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2228,131 +2304,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-33800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-9300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-10300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-11500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-13400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-11700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-23400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-10000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-10200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-8900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-8000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-6900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2374,8 +2459,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2397,67 +2483,71 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E41" s="3">
         <v>47900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>30100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>15600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>12600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>20900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>29000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>36300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>42500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>45900</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2483,7 +2573,7 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L42" s="3">
         <v>100</v>
@@ -2492,7 +2582,7 @@
         <v>100</v>
       </c>
       <c r="N42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -2509,62 +2599,65 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>4</v>
+      <c r="T42" s="3">
+        <v>0</v>
       </c>
       <c r="U42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E43" s="3">
         <v>4600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1200</v>
-      </c>
-      <c r="H43" s="3">
-        <v>400</v>
       </c>
       <c r="I43" s="3">
         <v>400</v>
       </c>
       <c r="J43" s="3">
+        <v>400</v>
+      </c>
+      <c r="K43" s="3">
         <v>1000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>100</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2574,47 +2667,50 @@
       <c r="U43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>800</v>
+      </c>
+      <c r="E44" s="3">
         <v>300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>200</v>
-      </c>
-      <c r="K44" s="3">
-        <v>600</v>
       </c>
       <c r="L44" s="3">
         <v>600</v>
       </c>
       <c r="M44" s="3">
+        <v>600</v>
+      </c>
+      <c r="N44" s="3">
         <v>400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>100</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
@@ -2633,8 +2729,11 @@
       <c r="U44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2645,13 +2744,13 @@
         <v>3800</v>
       </c>
       <c r="F45" s="3">
+        <v>3800</v>
+      </c>
+      <c r="G45" s="3">
         <v>9800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12200</v>
-      </c>
-      <c r="H45" s="3">
-        <v>8400</v>
       </c>
       <c r="I45" s="3">
         <v>8400</v>
@@ -2660,7 +2759,7 @@
         <v>8400</v>
       </c>
       <c r="K45" s="3">
-        <v>200</v>
+        <v>8400</v>
       </c>
       <c r="L45" s="3">
         <v>200</v>
@@ -2668,91 +2767,97 @@
       <c r="M45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>4</v>
+      <c r="N45" s="3">
+        <v>200</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="3">
         <v>900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>400</v>
-      </c>
-      <c r="T45" s="3">
-        <v>1800</v>
       </c>
       <c r="U45" s="3">
         <v>1800</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>53400</v>
+      </c>
+      <c r="E46" s="3">
         <v>63100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>41500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>29500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>23300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>30500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>15500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>18400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>14400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>13700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>21700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>29900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>36800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>44400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>47700</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2777,24 +2882,24 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>300</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L47" s="3">
         <v>300</v>
       </c>
       <c r="M47" s="3">
+        <v>300</v>
+      </c>
+      <c r="N47" s="3">
         <v>1600</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P47" s="3">
         <v>6100</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
@@ -2810,72 +2915,78 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E48" s="3">
         <v>59500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>59200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>54200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>52400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>53300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>53800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>54800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>74000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>72400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>69400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>38300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>33000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>30100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>28200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>19100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>16000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>12000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E49" s="3">
         <v>800</v>
@@ -2887,7 +2998,7 @@
         <v>800</v>
       </c>
       <c r="H49" s="3">
-        <v>4500</v>
+        <v>800</v>
       </c>
       <c r="I49" s="3">
         <v>4500</v>
@@ -2896,7 +3007,7 @@
         <v>4500</v>
       </c>
       <c r="K49" s="3">
-        <v>4600</v>
+        <v>4500</v>
       </c>
       <c r="L49" s="3">
         <v>4600</v>
@@ -2905,7 +3016,7 @@
         <v>4600</v>
       </c>
       <c r="N49" s="3">
-        <v>3900</v>
+        <v>4600</v>
       </c>
       <c r="O49" s="3">
         <v>3900</v>
@@ -2920,7 +3031,7 @@
         <v>3900</v>
       </c>
       <c r="S49" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="T49" s="3">
         <v>3800</v>
@@ -2928,8 +3039,11 @@
       <c r="U49" s="3">
         <v>3800</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2987,8 +3101,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3046,8 +3163,11 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3081,12 +3201,12 @@
       <c r="M52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N52" s="3">
+      <c r="N52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O52" s="3">
         <v>27700</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3105,8 +3225,11 @@
       <c r="U52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3164,67 +3287,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>119400</v>
+      </c>
+      <c r="E54" s="3">
         <v>123300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>101500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>84500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>76500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>88300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>73800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>77700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>89300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>88900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>83900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>74700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>57400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>47600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>53800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>52900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>56600</v>
-      </c>
-      <c r="T54" s="3">
-        <v>60200</v>
       </c>
       <c r="U54" s="3">
         <v>60200</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3">
+        <v>60200</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3246,8 +3375,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3269,67 +3399,71 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>900</v>
+      </c>
+      <c r="E57" s="3">
         <v>400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3340,38 +3474,38 @@
         <v>100</v>
       </c>
       <c r="F58" s="3">
+        <v>100</v>
+      </c>
+      <c r="G58" s="3">
         <v>7800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>10300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>16400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>17400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>100</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>4</v>
       </c>
@@ -3387,49 +3521,52 @@
       <c r="U58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>200</v>
+      </c>
+      <c r="E59" s="3">
         <v>100</v>
       </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
       <c r="F59" s="3">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3">
         <v>300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4400</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P59" s="3">
-        <v>100</v>
+      <c r="P59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q59" s="3">
         <v>100</v>
@@ -3438,75 +3575,81 @@
         <v>100</v>
       </c>
       <c r="S59" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="T59" s="3">
         <v>300</v>
       </c>
       <c r="U59" s="3">
+        <v>300</v>
+      </c>
+      <c r="V59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E60" s="3">
         <v>4200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>17400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>15800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>17000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>22300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>23000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>13700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3514,7 +3657,7 @@
         <v>100</v>
       </c>
       <c r="E61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F61" s="3">
         <v>200</v>
@@ -3523,11 +3666,11 @@
         <v>200</v>
       </c>
       <c r="H61" s="3">
+        <v>200</v>
+      </c>
+      <c r="I61" s="3">
         <v>300</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -3538,16 +3681,16 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>1700</v>
-      </c>
-      <c r="N61" s="3">
-        <v>100</v>
       </c>
       <c r="O61" s="3">
         <v>100</v>
       </c>
       <c r="P61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q61" s="3">
         <v>0</v>
@@ -3564,8 +3707,11 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3584,20 +3730,20 @@
       <c r="H62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3">
         <v>4500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2200</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>4</v>
+      <c r="M62" s="3">
+        <v>0</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>4</v>
@@ -3605,14 +3751,14 @@
       <c r="O62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P62" s="3">
-        <v>100</v>
+      <c r="P62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q62" s="3">
         <v>100</v>
       </c>
       <c r="R62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S62" s="3">
         <v>200</v>
@@ -3620,11 +3766,14 @@
       <c r="T62" s="3">
         <v>200</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U62" s="3">
+        <v>200</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3682,8 +3831,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3741,8 +3893,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3800,67 +3955,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E66" s="3">
         <v>4400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>13900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>17700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>19200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>22300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>24700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3882,8 +4043,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3941,8 +4103,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4000,8 +4165,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4054,13 +4222,16 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
         <v>300</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4118,67 +4289,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-313500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-279700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-270400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-260100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-249900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-238400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-225000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-213300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-189900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-176500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-167200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-160800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-152900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-147300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-141100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-138600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-131800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-129200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-125100</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4236,8 +4413,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4295,8 +4475,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4354,67 +4537,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>112800</v>
+      </c>
+      <c r="E76" s="3">
         <v>119000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>96000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>70600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>65600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>70600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>59300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>61500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>70100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>66600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>59200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>60900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>53900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>45900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>47300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>49600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>52700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>55100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>57400</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4472,131 +4661,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-33800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-9300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-10300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-11500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-13400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-11700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-23400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-10000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-10200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-8900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-8000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-6900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4618,8 +4816,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4630,10 +4829,10 @@
         <v>1300</v>
       </c>
       <c r="F83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G83" s="3">
         <v>1600</v>
-      </c>
-      <c r="G83" s="3">
-        <v>100</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
@@ -4648,17 +4847,17 @@
         <v>100</v>
       </c>
       <c r="L83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
       <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3">
         <v>100</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
       <c r="P83" s="3">
         <v>0</v>
       </c>
@@ -4677,8 +4876,11 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4736,8 +4938,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4795,8 +5000,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4854,8 +5062,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4913,8 +5124,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4972,67 +5186,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-9800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-7100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-10300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4000</v>
-      </c>
-      <c r="R89" s="3">
-        <v>-2900</v>
       </c>
       <c r="S89" s="3">
         <v>-2900</v>
       </c>
       <c r="T89" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="U89" s="3">
         <v>-1700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5054,67 +5274,71 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-700</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-500</v>
       </c>
       <c r="G91" s="3">
         <v>-500</v>
       </c>
       <c r="H91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I91" s="3">
         <v>-600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-6100</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-4100</v>
       </c>
       <c r="R91" s="3">
         <v>-4100</v>
       </c>
       <c r="S91" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="T91" s="3">
         <v>-3800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5172,8 +5396,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5231,67 +5458,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-700</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-500</v>
       </c>
       <c r="G94" s="3">
         <v>-500</v>
       </c>
       <c r="H94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I94" s="3">
         <v>-600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-7300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-18700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-7800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6100</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>-4100</v>
       </c>
       <c r="R94" s="3">
         <v>-4100</v>
       </c>
       <c r="S94" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="T94" s="3">
         <v>-3800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5313,8 +5546,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5354,8 +5588,8 @@
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5372,8 +5606,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5431,8 +5668,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5490,8 +5730,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5549,67 +5792,73 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>29100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>26300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>11000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>22800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>5200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>6900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>8500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>15100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>11000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>12400</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>-300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>500</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>41200</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5649,8 +5898,8 @@
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -5667,63 +5916,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E102" s="3">
         <v>17800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>18400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-12800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>14900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-10300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-8100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-7300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-6200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>33100</v>
       </c>
     </row>
